--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Test ID</t>
   </si>
@@ -22,13 +22,25 @@
     <t>Test Name</t>
   </si>
   <si>
+    <t>Priority</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Execution Time (ms)</t>
-  </si>
-  <si>
-    <t>Priority</t>
+    <t>Execution Time</t>
+  </si>
+  <si>
+    <t>Failure Reason</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>No failures — 100% pass rate ✅</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
 </sst>
 </file>
@@ -45,7 +57,8 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,7 +70,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="991B1B"/>
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +88,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,18 +430,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,6 +459,32 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,20 +34,48 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>No failures — 100% pass rate ✅</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>TC-SEL-LOGIN-001</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>Login page title is non-empty"</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
+  (Session info: chrome=151.0.7922.140)</t>
+  </si>
+  <si>
+    <t>TC-SEL-REG-001</t>
+  </si>
+  <si>
+    <t>register</t>
+  </si>
+  <si>
+    <t>Register page loads successfully"</t>
+  </si>
+  <si>
+    <t>TC-SEL-DONOR-001</t>
+  </si>
+  <si>
+    <t>donor</t>
+  </si>
+  <si>
+    <t>Donor dashboard route loads without crash"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -60,8 +88,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF991B1B"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -71,6 +103,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDC2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,11 +123,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -469,22 +507,68 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>21094</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>5734</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>3453</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
